--- a/src/New-release-old/GVA OPH HW.xlsx
+++ b/src/New-release-old/GVA OPH HW.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\visualisations\dvc3200-3299\dvc3221-productivityflash\fig7\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://officenationalstatistics.sharepoint.com/sites/msdfp/fp/FLOVERVIEW/Floverview + LCLI 2025 IndQ1 - 2025 WEQ2/Figures/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED73DFA8-7732-411E-AF5B-52540997517D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_C5936EB912B9B29E9092EA83F2DB4D79071F2031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D80DA399-4A35-4C7E-B3A8-CE47BC0207D3}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{C356E194-D702-436B-9000-A9EFE78F410C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Data for Dataviz" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -38,10 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
-    <t>Figure 7: In 2024 the construction and IT industries output per hour grew by 16.2% and 15.4% respectively in comparison with 2019</t>
-  </si>
-  <si>
-    <t>Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), 2024 compared with 2019, UK</t>
+    <t>Figure 7: In 2025Q1 the agriculture, forestry and fishing industry and the IT industry saw output per hour grow by 32.1% and 18.2% respectively in comparison with 2019 average</t>
+  </si>
+  <si>
+    <t>Decomposition of growth of output per hour worked, hours worked and gross value added (GVA), Quarter 1 (Jan to Mar) 2025 compared with 2019 average, percentage change, UK</t>
   </si>
   <si>
     <t>Notes</t>
@@ -59,6 +59,9 @@
     <t>GVA</t>
   </si>
   <si>
+    <t>Hours worked (sign reversed)</t>
+  </si>
+  <si>
     <t>Output per hour worked</t>
   </si>
   <si>
@@ -120,22 +123,19 @@
   </si>
   <si>
     <t>ST: Other Services</t>
-  </si>
-  <si>
-    <t>Hours worked</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -166,21 +166,20 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{772E8716-2135-4F66-BA00-78F64245A391}"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -209,13 +208,13 @@
         <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="145F82"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="E87331"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="186C24"/>
       </a:accent3>
       <a:accent4>
         <a:srgbClr val="0F9ED5"/>
@@ -235,7 +234,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -501,385 +500,392 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C3893B8-1A18-4E87-8F1E-D3AF39595E16}">
-  <dimension ref="A1:E27"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F044E81-6507-406E-A706-F956F5590C89}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="25" style="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>4.5585458740000001E-2</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.4982880039999999E-2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2.0100412500000001E-2</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>5.0971763839999996E-2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>-0.2040935864</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0.32047153530000005</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>-0.37187524799999999</v>
+      </c>
+      <c r="C10" s="3">
+        <v>-0.25948556789999999</v>
+      </c>
+      <c r="D10" s="3">
+        <v>-0.1517724372</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>-1.9522724499999998E-3</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-7.0904024019999998E-2</v>
+      </c>
+      <c r="D11" s="3">
+        <v>7.4213809290000002E-2</v>
+      </c>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>-0.1918053156</v>
+      </c>
+      <c r="C12" s="3">
+        <v>4.0490321899999994E-3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>-0.19506452530000001</v>
+      </c>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>7.6667720519999996E-2</v>
+      </c>
+      <c r="C13" s="3">
+        <v>7.2726417540000005E-2</v>
+      </c>
+      <c r="D13" s="3">
+        <v>3.67409892E-3</v>
+      </c>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="3">
+        <v>8.4416862179999996E-2</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-7.6469758590000006E-2</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0.1742082864</v>
+      </c>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="3">
+        <v>-3.6905394629999998E-2</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-5.0819763980000002E-2</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1.4659354280000002E-2</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1.293155155E-2</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-1.5494349670000001E-2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>2.8873273809999999E-2</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="3">
+        <v>-9.0305956219999997E-2</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2.2233416759999999E-2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>-0.1100916592</v>
+      </c>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.22816911009999999</v>
+      </c>
+      <c r="C18" s="3">
+        <v>3.9332660979999996E-2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0.18169009419999999</v>
+      </c>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19" s="3">
+        <v>-2.117585822E-2</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4.1132686889999999E-2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>-5.9846882050000001E-2</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3">
+        <v>-1.543290609E-2</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.19499248470000002</v>
+      </c>
+      <c r="D20" s="3">
+        <v>-0.17608930050000002</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.17434358320000001</v>
+      </c>
+      <c r="C21" s="3">
+        <v>8.3591284229999993E-2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>8.3751410969999995E-2</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.14905226620000001</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.7576140990000001E-2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0.11821617919999999</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.1132313298</v>
+      </c>
+      <c r="C23" s="3">
+        <v>0.14618718040000001</v>
+      </c>
+      <c r="D23" s="3">
+        <v>-2.8752590509999999E-2</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.1043282187</v>
+      </c>
+      <c r="C24" s="3">
+        <v>5.9720959779999999E-2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>4.2093400599999997E-2</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3">
+        <v>-2.2378474759999999E-2</v>
+      </c>
+      <c r="C25" s="3">
+        <v>0.1736830264</v>
+      </c>
+      <c r="D25" s="3">
+        <v>-0.16704808430000001</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26" s="3">
+        <v>-8.4224313869999998E-2</v>
+      </c>
+      <c r="C26" s="3">
+        <v>1.5980577410000002E-2</v>
+      </c>
+      <c r="D26" s="3">
+        <v>-9.8628746959999999E-2</v>
+      </c>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3.6847492323439042E-2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1.783944499504457E-2</v>
-      </c>
-      <c r="D8" s="2">
-        <v>1.7543859649122688E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2">
-        <v>3.3639143730886965E-2</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-0.1263507896924356</v>
-      </c>
-      <c r="D9" s="2">
-        <v>0.18404907975460122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2">
-        <v>-0.34971796937953259</v>
-      </c>
-      <c r="C10" s="2">
-        <v>-0.17777777777777778</v>
-      </c>
-      <c r="D10" s="2">
-        <v>-0.20942883046237529</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2">
-        <v>-7.8585461689587143E-3</v>
-      </c>
-      <c r="C11" s="2">
-        <v>-6.2499999999999951E-2</v>
-      </c>
-      <c r="D11" s="2">
-        <v>5.8091286307053881E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B12" s="2">
-        <v>-0.20874152223059525</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-7.0347284060552018E-2</v>
-      </c>
-      <c r="D12" s="2">
-        <v>-0.1490262489415749</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2">
-        <v>2.0255863539445692E-2</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0.10819327731092433</v>
-      </c>
-      <c r="D13" s="2">
-        <v>-7.9187817258883214E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="2">
-        <v>7.6359832635983393E-2</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-7.2945521698984231E-2</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0.16213151927437638</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2">
-        <v>-5.0620821394460336E-2</v>
-      </c>
-      <c r="C15" s="2">
-        <v>-3.8606403013182751E-2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-1.4184397163120624E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="2">
-        <v>9.8039215686268936E-4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>-2.3506366307541545E-2</v>
-      </c>
-      <c r="D16" s="2">
-        <v>2.4000000000000056E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="2">
-        <v>-7.879377431906609E-2</v>
-      </c>
-      <c r="C17" s="2">
-        <v>-2.5242718446601888E-2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>-5.5110220440881763E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2">
-        <v>0.18883610451306401</v>
-      </c>
-      <c r="C18" s="2">
-        <v>2.9804727646454324E-2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>0.15357967667436503</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="2">
-        <v>-1.1022044088176296E-2</v>
-      </c>
-      <c r="C19" s="2">
-        <v>2.3715415019762761E-2</v>
-      </c>
-      <c r="D19" s="2">
-        <v>-3.248730964467008E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="2">
-        <v>-1.0351966873706004E-2</v>
-      </c>
-      <c r="C20" s="2">
-        <v>0.1837606837606838</v>
-      </c>
-      <c r="D20" s="2">
-        <v>-0.16375968992248066</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2">
-        <v>0.161036036036036</v>
-      </c>
-      <c r="C21" s="2">
-        <v>8.3418107833163821E-2</v>
-      </c>
-      <c r="D21" s="2">
-        <v>7.1982281284606875E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2">
-        <v>0.11943319838056678</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1.0256410256410256E-2</v>
-      </c>
-      <c r="D22" s="2">
-        <v>0.10858835143139191</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2">
-        <v>9.5789473684210466E-2</v>
-      </c>
-      <c r="C23" s="2">
-        <v>0.13297297297297295</v>
-      </c>
-      <c r="D23" s="2">
-        <v>-3.310613437195721E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2">
-        <v>0.11431623931623935</v>
-      </c>
-      <c r="C24" s="2">
-        <v>4.4057377049180446E-2</v>
-      </c>
-      <c r="D24" s="2">
-        <v>6.6736183524504597E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="2">
-        <v>-3.2317636195752543E-2</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0.144973544973545</v>
-      </c>
-      <c r="D25" s="2">
-        <v>-0.15445026178010463</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="2">
-        <v>-7.735849056603776E-2</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1.3752455795677855E-2</v>
-      </c>
-      <c r="D26" s="2">
-        <v>-8.9337175792507176E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2">
-        <v>-3.2075471698113263E-2</v>
-      </c>
-      <c r="C27" s="2">
-        <v>1.6377649325626232E-2</v>
-      </c>
-      <c r="D27" s="2">
-        <v>-4.7012732615083229E-2</v>
-      </c>
+      <c r="B27" s="3">
+        <v>7.4499418399999991E-3</v>
+      </c>
+      <c r="C27" s="3">
+        <v>8.6685475000000001E-3</v>
+      </c>
+      <c r="D27" s="3">
+        <v>-1.20813291E-3</v>
+      </c>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E0CEF6E26CBF2C4F8000DAAA032CD586" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4b00db03ba10acd9ce0de4b8508f462a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8a54c791-04d1-4dd7-97a3-a882d4048403" xmlns:ns3="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="93f033296de2705646020d6024e1f2eb" ns2:_="" ns3:_="">
     <xsd:import namespace="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
@@ -1128,6 +1134,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1140,15 +1155,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43BE88E2-2E27-4E07-81F0-9A0A4E6B2A7F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A71E7A-4217-4997-B8EB-D76FCFA58B33}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1D3EC00-AF65-4EBB-B8FA-08CAA55E16F6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -1166,13 +1173,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CFF1937A-CB3E-495A-B59F-005F61E111B9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E742F0C-7D8D-4BE2-8E80-BDE399066E8B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3DA9672E-0F58-416B-8B3A-FA7330BAA036}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="8a54c791-04d1-4dd7-97a3-a882d4048403"/>
-    <ds:schemaRef ds:uri="7c97fbf4-89e8-4607-8aa6-eba0d12e3a2a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>